--- a/artfynd/A 30090-2024 artfynd.xlsx
+++ b/artfynd/A 30090-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117323618</v>
+        <v>117323658</v>
       </c>
       <c r="B2" t="n">
-        <v>4860</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101675</v>
+        <v>101186</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Aspsplintbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Leiopus punctulatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Paykull, 1800)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603734</v>
+        <v>603783</v>
       </c>
       <c r="R2" t="n">
-        <v>6671957</v>
+        <v>6671905</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +769,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>aspstam</t>
+          <t>aspgren med svart röta</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,37 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117323658</v>
+        <v>117323618</v>
       </c>
       <c r="B3" t="n">
-        <v>5270</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101186</v>
+        <v>101675</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aspsplintbock</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leiopus punctulatus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Paykull, 1800)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603783</v>
+        <v>603734</v>
       </c>
       <c r="R3" t="n">
-        <v>6671905</v>
+        <v>6671957</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,7 +881,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>aspgren med svart röta</t>
+          <t>aspstam</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -912,12 +902,7 @@
         <v>117323617</v>
       </c>
       <c r="B4" t="n">
-        <v>43657</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,12 +1014,7 @@
         <v>117323659</v>
       </c>
       <c r="B5" t="n">
-        <v>8405</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30090-2024 artfynd.xlsx
+++ b/artfynd/A 30090-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117323658</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117323618</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117323617</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,8 +1140,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117323659</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>